--- a/Assets/Localization/翻译文本/CollectedLocalizeData.xlsx
+++ b/Assets/Localization/翻译文本/CollectedLocalizeData.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="208">
   <si>
     <t>#var</t>
   </si>
@@ -26,7 +26,7 @@
     <t>lTips2</t>
   </si>
   <si>
-    <t>zh-cn</t>
+    <t>zh-CN</t>
   </si>
   <si>
     <t>en</t>
@@ -35,6 +35,9 @@
     <t>ja</t>
   </si>
   <si>
+    <t>zh-CHT</t>
+  </si>
+  <si>
     <t>#type</t>
   </si>
   <si>
@@ -44,6 +47,9 @@
     <t>Item.Name.E01.1_法医_死因</t>
   </si>
   <si>
+    <t>AI</t>
+  </si>
+  <si>
     <t>死者死于失温</t>
   </si>
   <si>
@@ -53,6 +59,9 @@
     <t>死者は低体温症で死亡</t>
   </si>
   <si>
+    <t>死者死於失溫</t>
+  </si>
+  <si>
     <t>Item.Name.E01.2_法医_死亡时间</t>
   </si>
   <si>
@@ -65,6 +74,9 @@
     <t>死者の死亡時間は午前0時から2時の間</t>
   </si>
   <si>
+    <t>死者死亡時間在凌晨0點至2點之間</t>
+  </si>
+  <si>
     <t>Item.Name.E02_死者_冷库痕迹</t>
   </si>
   <si>
@@ -77,6 +89,9 @@
     <t>死者の靴底には冷蔵庫専用の滑り止め粉が付着</t>
   </si>
   <si>
+    <t>死者鞋底沾有冷庫專用防滑粉</t>
+  </si>
+  <si>
     <t>Item.Name.E03_法医_指甲金属</t>
   </si>
   <si>
@@ -89,6 +104,9 @@
     <t>死者の爪の間に灰色の金属塗料が残留</t>
   </si>
   <si>
+    <t>死者指甲縫中殘留灰色金屬漆</t>
+  </si>
+  <si>
     <t>Item.Name.E03_法医_死者手掌</t>
   </si>
   <si>
@@ -101,6 +119,9 @@
     <t>死者は低温物体に直接接触</t>
   </si>
   <si>
+    <t>死者直接接觸了低溫物體</t>
+  </si>
+  <si>
     <t>Item.Name.E04_警察_后门货车</t>
   </si>
   <si>
@@ -113,6 +134,9 @@
     <t>深夜にバンが公園の裏口に駐車</t>
   </si>
   <si>
+    <t>深夜有廂式貨車停在公園後門</t>
+  </si>
+  <si>
     <t>Item.Name.E05.1_警察_家庭时间线</t>
   </si>
   <si>
@@ -125,6 +149,9 @@
     <t>23:00頃、一家三口が公園で激しい口論</t>
   </si>
   <si>
+    <t>23:00左右，一家三口在公園激烈爭吵</t>
+  </si>
+  <si>
     <t>Item.Name.E05.2_警察_家庭时间线</t>
   </si>
   <si>
@@ -137,6 +164,9 @@
     <t>00:00頃、死者と小三花が単独で離れ、小三花のみが戻る</t>
   </si>
   <si>
+    <t>00:00左右，死者與小三花單獨離開，僅小三花返回</t>
+  </si>
+  <si>
     <t>Item.Name.E06_大强_认罪</t>
   </si>
   <si>
@@ -149,6 +179,9 @@
     <t>シャムは死者が湖に誤って転落したと主張</t>
   </si>
   <si>
+    <t>暹羅聲稱死者為意外跌落湖中</t>
+  </si>
+  <si>
     <t>Item.Name.E08.1_死者手机_草稿</t>
   </si>
   <si>
@@ -161,6 +194,9 @@
     <t>死者の携帯電話には、橘猫に離婚を迫り秘密を暴露する脅迫文の下書きが保存</t>
   </si>
   <si>
+    <t>死者手機中存有威脅橘貓離婚並揭發其秘密的草稿</t>
+  </si>
+  <si>
     <t>Item.Name.E08.2_死者手机_通话</t>
   </si>
   <si>
@@ -173,6 +209,9 @@
     <t>0:31、死者と橘猫の通話記録あり</t>
   </si>
   <si>
+    <t>0:31，死者與橘貓有過通話記錄</t>
+  </si>
+  <si>
     <t>Item.Name.E09_货车_温度</t>
   </si>
   <si>
@@ -185,6 +224,9 @@
     <t>01:28から02:54、車内温度はマイナス18度を維持</t>
   </si>
   <si>
+    <t>01:28至02:54，車廂溫度維持在零下18度</t>
+  </si>
+  <si>
     <t>Item.Name.E10_货车_抓痕</t>
   </si>
   <si>
@@ -197,6 +239,9 @@
     <t>バン内に明らかな引っかき傷</t>
   </si>
   <si>
+    <t>貨車內有明顯的抓痕</t>
+  </si>
+  <si>
     <t>Item.Name.E10_货车_车厢</t>
   </si>
   <si>
@@ -209,6 +254,9 @@
     <t>01:04から03:05、バンが公園の裏口に2回出現</t>
   </si>
   <si>
+    <t>01:04至03:05，貨車兩次出現在公園後門</t>
+  </si>
+  <si>
     <t>Item.Name.E11_警察_货车搜查令</t>
   </si>
   <si>
@@ -221,6 +269,9 @@
     <t>橘猫のバンと携帯電話を調査可能</t>
   </si>
   <si>
+    <t>可以調查橘貓的貨車和手機了</t>
+  </si>
+  <si>
     <t>Item.Name.E11_遗物_修改受益人</t>
   </si>
   <si>
@@ -233,6 +284,9 @@
     <t>死者は保険の受取人を橘猫に変更する計画</t>
   </si>
   <si>
+    <t>死者計劃將保險受益人改給橘貓</t>
+  </si>
+  <si>
     <t>Item.Name.E11_遗物_受益人</t>
   </si>
   <si>
@@ -245,6 +299,9 @@
     <t>死者の200万保険の受取人は小三花</t>
   </si>
   <si>
+    <t>死者的200萬保險受益人是小三花</t>
+  </si>
+  <si>
     <t>Character.Name.死者</t>
   </si>
   <si>
@@ -266,6 +323,9 @@
     <t>死者の携帯電話</t>
   </si>
   <si>
+    <t>死者手機</t>
+  </si>
+  <si>
     <t>Character.Name.你</t>
   </si>
   <si>
@@ -290,6 +350,9 @@
     <t>コンビニのバン</t>
   </si>
   <si>
+    <t>便利店貨車</t>
+  </si>
+  <si>
     <t>Character.Name.公园轮胎印迹</t>
   </si>
   <si>
@@ -302,6 +365,9 @@
     <t>公園のタイヤ痕</t>
   </si>
   <si>
+    <t>公園輪胎印跡</t>
+  </si>
+  <si>
     <t>Character.Name.奶牛警察</t>
   </si>
   <si>
@@ -335,6 +401,9 @@
     <t>通報者</t>
   </si>
   <si>
+    <t>報案人</t>
+  </si>
+  <si>
     <t>Character.Name.暹罗</t>
   </si>
   <si>
@@ -347,6 +416,9 @@
     <t>シャム</t>
   </si>
   <si>
+    <t>暹羅</t>
+  </si>
+  <si>
     <t>Character.Name.橘猫</t>
   </si>
   <si>
@@ -356,6 +428,9 @@
     <t>Orange Cat</t>
   </si>
   <si>
+    <t>橘貓</t>
+  </si>
+  <si>
     <t>Character.Name.橘猫手机</t>
   </si>
   <si>
@@ -368,6 +443,9 @@
     <t>橘猫の携帯電話</t>
   </si>
   <si>
+    <t>橘貓手機</t>
+  </si>
+  <si>
     <t>Character.Name.死者遗物</t>
   </si>
   <si>
@@ -380,6 +458,9 @@
     <t>死者の遺品</t>
   </si>
   <si>
+    <t>死者遺物</t>
+  </si>
+  <si>
     <t>Character.Name.白猫</t>
   </si>
   <si>
@@ -389,6 +470,9 @@
     <t>White Cat</t>
   </si>
   <si>
+    <t>白貓</t>
+  </si>
+  <si>
     <t>Character.Name.路人A</t>
   </si>
   <si>
@@ -434,6 +518,9 @@
     <t>読み込み</t>
   </si>
   <si>
+    <t>載入</t>
+  </si>
+  <si>
     <t>UI.SavePanel.Reset</t>
   </si>
   <si>
@@ -447,9 +534,6 @@
   </si>
   <si>
     <t>UI.Dice.DetailText</t>
-  </si>
-  <si>
-    <t>AI</t>
   </si>
   <si>
     <t xml:space="preserve">难度: &lt;b&gt;{0}&lt;/b&gt;    属性加成: &lt;b&gt;+{1}&lt;/b&gt;
@@ -464,6 +548,10 @@
  &lt;size=80%&gt;D{2} + {3} ≥ {4} が必要&lt;/size&gt;</t>
   </si>
   <si>
+    <t xml:space="preserve">難度: &lt;b&gt;{0}&lt;/b&gt;    屬性加成: &lt;b&gt;+{1}&lt;/b&gt;
+ &lt;size=80%&gt;需要 D{2} + {3} ≥ {4}&lt;/size&gt;</t>
+  </si>
+  <si>
     <t>UI.Dice.RollAnim</t>
   </si>
   <si>
@@ -473,6 +561,10 @@
   <si>
     <t xml:space="preserve">&lt;size=150%&gt;&lt;b&gt;[ {0} ]&lt;/b&gt;&lt;/size&gt;
  D{1}: {0} + Attribute: {2} = {3}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;size=150%&gt;&lt;b&gt;[ {0} ]&lt;/b&gt;&lt;/size&gt;
+ D{1}: {0} + 屬性: {2} = {3}</t>
   </si>
   <si>
     <t>UI.Dice.RollResult</t>
@@ -493,6 +585,11 @@
  &lt;size=120%&gt;&lt;color={5}&gt;&lt;b&gt;— {6} —&lt;/b&gt;&lt;/color&gt;&lt;/size&gt;</t>
   </si>
   <si>
+    <t xml:space="preserve">&lt;size=150%&gt;&lt;b&gt;[ {0} ]&lt;/b&gt;&lt;/size&gt;
+ D{1}: &lt;b&gt;{0}&lt;/b&gt; + 屬性: &lt;b&gt;{2}&lt;/b&gt; = &lt;b&gt;{3}&lt;/b&gt;  (難度 {4})
+ &lt;size=120%&gt;&lt;color={5}&gt;&lt;b&gt;— {6} —&lt;/b&gt;&lt;/color&gt;&lt;/size&gt;</t>
+  </si>
+  <si>
     <t>UI.Common.Success</t>
   </si>
   <si>
@@ -526,6 +623,9 @@
     <t>ダイスロール</t>
   </si>
   <si>
+    <t>擲骰</t>
+  </si>
+  <si>
     <t>UI.Dice.ConfirmButton</t>
   </si>
   <si>
@@ -548,6 +648,9 @@
   </si>
   <si>
     <t>手がかりはありません</t>
+  </si>
+  <si>
+    <t>暫無線索</t>
   </si>
 </sst>
 </file>
@@ -593,7 +696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -618,651 +721,894 @@
       <c r="G1" s="0" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="0" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="H2" s="0" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>12</v>
+        <v>14</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="0" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="0" t="s">
-        <v>17</v>
+        <v>21</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="0" t="s">
-        <v>21</v>
+        <v>26</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>24</v>
+        <v>29</v>
+      </c>
+      <c r="H6" s="0" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="0" t="s">
-        <v>25</v>
+        <v>31</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>28</v>
+        <v>34</v>
+      </c>
+      <c r="H7" s="0" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="0" t="s">
-        <v>29</v>
+        <v>36</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
+      </c>
+      <c r="H8" s="0" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="0" t="s">
-        <v>33</v>
+        <v>41</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>36</v>
+        <v>44</v>
+      </c>
+      <c r="H9" s="0" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="0" t="s">
-        <v>37</v>
+        <v>46</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>40</v>
+        <v>49</v>
+      </c>
+      <c r="H10" s="0" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="0" t="s">
-        <v>41</v>
+        <v>51</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>44</v>
+        <v>54</v>
+      </c>
+      <c r="H11" s="0" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="0" t="s">
-        <v>45</v>
+        <v>56</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>48</v>
+        <v>59</v>
+      </c>
+      <c r="H12" s="0" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="0" t="s">
-        <v>49</v>
+        <v>61</v>
+      </c>
+      <c r="D13" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>52</v>
+        <v>64</v>
+      </c>
+      <c r="H13" s="0" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="0" t="s">
-        <v>53</v>
+        <v>66</v>
+      </c>
+      <c r="D14" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>56</v>
+        <v>69</v>
+      </c>
+      <c r="H14" s="0" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="0" t="s">
-        <v>57</v>
+        <v>71</v>
+      </c>
+      <c r="D15" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>60</v>
+        <v>74</v>
+      </c>
+      <c r="H15" s="0" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="0" t="s">
-        <v>61</v>
+        <v>76</v>
+      </c>
+      <c r="D16" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>64</v>
+        <v>79</v>
+      </c>
+      <c r="H16" s="0" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="0" t="s">
-        <v>65</v>
+        <v>81</v>
+      </c>
+      <c r="D17" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="G17" s="0" t="s">
-        <v>68</v>
+        <v>84</v>
+      </c>
+      <c r="H17" s="0" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="0" t="s">
-        <v>69</v>
+        <v>86</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="G18" s="0" t="s">
-        <v>72</v>
+        <v>89</v>
+      </c>
+      <c r="H18" s="0" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="0" t="s">
-        <v>73</v>
+        <v>91</v>
+      </c>
+      <c r="D19" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>76</v>
+        <v>94</v>
+      </c>
+      <c r="H19" s="0" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="0" t="s">
-        <v>77</v>
+        <v>96</v>
+      </c>
+      <c r="D20" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>78</v>
+        <v>97</v>
+      </c>
+      <c r="H20" s="0" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="0" t="s">
-        <v>80</v>
+        <v>99</v>
+      </c>
+      <c r="D21" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="G21" s="0" t="s">
-        <v>83</v>
+        <v>102</v>
+      </c>
+      <c r="H21" s="0" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="0" t="s">
-        <v>84</v>
+        <v>104</v>
+      </c>
+      <c r="D22" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>87</v>
+        <v>107</v>
+      </c>
+      <c r="H22" s="0" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="0" t="s">
-        <v>88</v>
+        <v>108</v>
+      </c>
+      <c r="D23" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="G23" s="0" t="s">
-        <v>91</v>
+        <v>111</v>
+      </c>
+      <c r="H23" s="0" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="0" t="s">
-        <v>92</v>
+        <v>113</v>
+      </c>
+      <c r="D24" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>95</v>
+        <v>116</v>
+      </c>
+      <c r="H24" s="0" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="0" t="s">
-        <v>96</v>
+        <v>118</v>
+      </c>
+      <c r="D25" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>99</v>
+        <v>121</v>
+      </c>
+      <c r="H25" s="0" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="0" t="s">
-        <v>100</v>
+        <v>122</v>
+      </c>
+      <c r="D26" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>101</v>
+        <v>123</v>
+      </c>
+      <c r="H26" s="0" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="0" t="s">
-        <v>103</v>
+        <v>125</v>
+      </c>
+      <c r="D27" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="G27" s="0" t="s">
-        <v>106</v>
+        <v>128</v>
+      </c>
+      <c r="H27" s="0" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="0" t="s">
-        <v>107</v>
+        <v>130</v>
+      </c>
+      <c r="D28" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="G28" s="0" t="s">
-        <v>110</v>
+        <v>133</v>
+      </c>
+      <c r="H28" s="0" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="0" t="s">
-        <v>111</v>
+        <v>135</v>
+      </c>
+      <c r="D29" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="G29" s="0" t="s">
-        <v>112</v>
+        <v>136</v>
+      </c>
+      <c r="H29" s="0" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="0" t="s">
-        <v>114</v>
+        <v>139</v>
+      </c>
+      <c r="D30" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="G30" s="0" t="s">
-        <v>117</v>
+        <v>142</v>
+      </c>
+      <c r="H30" s="0" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="0" t="s">
-        <v>118</v>
+        <v>144</v>
+      </c>
+      <c r="D31" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="G31" s="0" t="s">
-        <v>121</v>
+        <v>147</v>
+      </c>
+      <c r="H31" s="0" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="0" t="s">
-        <v>122</v>
+        <v>149</v>
+      </c>
+      <c r="D32" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="G32" s="0" t="s">
-        <v>123</v>
+        <v>150</v>
+      </c>
+      <c r="H32" s="0" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="0" t="s">
-        <v>125</v>
+        <v>153</v>
+      </c>
+      <c r="D33" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="G33" s="0" t="s">
-        <v>128</v>
+        <v>156</v>
+      </c>
+      <c r="H33" s="0" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="0" t="s">
-        <v>129</v>
+        <v>157</v>
+      </c>
+      <c r="D34" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E34" s="0" t="s">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="G34" s="0" t="s">
-        <v>132</v>
+        <v>160</v>
+      </c>
+      <c r="H34" s="0" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="0" t="s">
-        <v>133</v>
+        <v>161</v>
+      </c>
+      <c r="D35" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="G35" s="0" t="s">
-        <v>134</v>
+        <v>162</v>
+      </c>
+      <c r="H35" s="0" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="0" t="s">
-        <v>136</v>
+        <v>164</v>
+      </c>
+      <c r="D36" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="G36" s="0" t="s">
-        <v>139</v>
+        <v>167</v>
+      </c>
+      <c r="H36" s="0" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="0" t="s">
-        <v>140</v>
+        <v>169</v>
+      </c>
+      <c r="D37" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="F37" s="0" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="G37" s="0" t="s">
-        <v>143</v>
+        <v>172</v>
+      </c>
+      <c r="H37" s="0" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="0" t="s">
-        <v>144</v>
+        <v>173</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>145</v>
+        <v>11</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>146</v>
+        <v>174</v>
       </c>
       <c r="F38" s="0" t="s">
-        <v>147</v>
+        <v>175</v>
       </c>
       <c r="G38" s="0" t="s">
-        <v>148</v>
+        <v>176</v>
+      </c>
+      <c r="H38" s="0" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="0" t="s">
-        <v>149</v>
+        <v>178</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>145</v>
+        <v>11</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>150</v>
+        <v>179</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
       <c r="G39" s="0" t="s">
-        <v>150</v>
+        <v>179</v>
+      </c>
+      <c r="H39" s="0" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="0" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>145</v>
+        <v>11</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="G40" s="0" t="s">
-        <v>155</v>
+        <v>185</v>
+      </c>
+      <c r="H40" s="0" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="0" t="s">
-        <v>156</v>
+        <v>187</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>145</v>
+        <v>11</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="F41" s="0" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="G41" s="0" t="s">
-        <v>157</v>
+        <v>188</v>
+      </c>
+      <c r="H41" s="0" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="0" t="s">
-        <v>159</v>
+        <v>190</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>145</v>
+        <v>11</v>
       </c>
       <c r="E42" s="0" t="s">
-        <v>160</v>
+        <v>191</v>
       </c>
       <c r="F42" s="0" t="s">
-        <v>161</v>
+        <v>192</v>
       </c>
       <c r="G42" s="0" t="s">
-        <v>162</v>
+        <v>193</v>
+      </c>
+      <c r="H42" s="0" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="0" t="s">
-        <v>163</v>
+        <v>194</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>145</v>
+        <v>11</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="G43" s="0" t="s">
-        <v>166</v>
+        <v>197</v>
+      </c>
+      <c r="H43" s="0" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="0" t="s">
-        <v>167</v>
+        <v>199</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>145</v>
+        <v>11</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>168</v>
+        <v>200</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="G44" s="0" t="s">
-        <v>170</v>
+        <v>202</v>
+      </c>
+      <c r="H44" s="0" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="0" t="s">
-        <v>171</v>
+        <v>203</v>
+      </c>
+      <c r="D45" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="G45" s="0" t="s">
-        <v>174</v>
+        <v>206</v>
+      </c>
+      <c r="H45" s="0" t="s">
+        <v>207</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Localization/翻译文本/CollectedLocalizeData.xlsx
+++ b/Assets/Localization/翻译文本/CollectedLocalizeData.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="213">
   <si>
     <t>#var</t>
   </si>
@@ -23,12 +23,12 @@
     <t>lTips1</t>
   </si>
   <si>
+    <t>zh-CN</t>
+  </si>
+  <si>
     <t>lTips2</t>
   </si>
   <si>
-    <t>zh-CN</t>
-  </si>
-  <si>
     <t>en</t>
   </si>
   <si>
@@ -47,9 +47,6 @@
     <t>Item.Name.E01.1_法医_死因</t>
   </si>
   <si>
-    <t>AI</t>
-  </si>
-  <si>
     <t>死者死于失温</t>
   </si>
   <si>
@@ -497,6 +494,21 @@
     <t>通行人B</t>
   </si>
   <si>
+    <t>Glossary.1</t>
+  </si>
+  <si>
+    <t>福尔摩斯</t>
+  </si>
+  <si>
+    <t>Sherlock Holmes</t>
+  </si>
+  <si>
+    <t>ホームズ</t>
+  </si>
+  <si>
+    <t>福爾摩斯</t>
+  </si>
+  <si>
     <t>UI.SavePanel.Save</t>
   </si>
   <si>
@@ -536,20 +548,16 @@
     <t>UI.Dice.DetailText</t>
   </si>
   <si>
-    <t xml:space="preserve">难度: &lt;b&gt;{0}&lt;/b&gt;    属性加成: &lt;b&gt;+{1}&lt;/b&gt;
- &lt;size=80%&gt;需要 D{2} + {3} ≥ {4}&lt;/size&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Difficulty: &lt;b&gt;{0}&lt;/b&gt;    Attribute Bonus: &lt;b&gt;+{1}&lt;/b&gt;
- &lt;size=80%&gt;Requires D{2} + {3} ≥ {4}&lt;/size&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">難易度: &lt;b&gt;{0}&lt;/b&gt;    属性ボーナス: &lt;b&gt;+{1}&lt;/b&gt;
- &lt;size=80%&gt;D{2} + {3} ≥ {4} が必要&lt;/size&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">難度: &lt;b&gt;{0}&lt;/b&gt;    屬性加成: &lt;b&gt;+{1}&lt;/b&gt;
- &lt;size=80%&gt;需要 D{2} + {3} ≥ {4}&lt;/size&gt;</t>
+    <t xml:space="preserve">难度: &lt;b&gt;{0}&lt;/b&gt;    属性加成: &lt;b&gt;+{1}&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Difficulty: &lt;b&gt;{0}&lt;/b&gt;    Attribute Bonus: &lt;b&gt;+{1}&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">難易度: &lt;b&gt;{0}&lt;/b&gt;    属性ボーナス: &lt;b&gt;+{1}&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">難度: &lt;b&gt;{0}&lt;/b&gt;    屬性加成: &lt;b&gt;+{1}&lt;/b&gt;</t>
   </si>
   <si>
     <t>UI.Dice.RollAnim</t>
@@ -570,24 +578,34 @@
     <t>UI.Dice.RollResult</t>
   </si>
   <si>
+    <t xml:space="preserve">修改:[&lt;size=150%&gt;&lt;b&gt;[ {0} ]&lt;/b&gt;&lt;/size&gt;\n &lt;b&gt;{0}&lt;/b&gt; + &lt;b&gt;{1}&lt;/b&gt; = &lt;b&gt;{2}&lt;/b&gt;  \n(难度 {3}) \n&lt;size=120%&gt;&lt;color={4}&gt;&lt;b&gt;— {5} —&lt;/b&gt;&lt;/color&gt;&lt;/size&gt;]-&gt;[&lt;size=150%&gt;&lt;b&gt;[ {0} ]&lt;/b&gt;&lt;/size&gt;
+ &lt;b&gt;{0}&lt;/b&gt; + &lt;b&gt;{1}&lt;/b&gt; = &lt;b&gt;{2}&lt;/b&gt; 
+(难度 {3}) 
+&lt;size=120%&gt;&lt;color={4}&gt;&lt;b&gt;— {5} —&lt;/b&gt;&lt;/color&gt;&lt;/size&gt;] 2026/2/26</t>
+  </si>
+  <si>
     <t xml:space="preserve">&lt;size=150%&gt;&lt;b&gt;[ {0} ]&lt;/b&gt;&lt;/size&gt;
- D{1}: &lt;b&gt;{0}&lt;/b&gt; + 属性: &lt;b&gt;{2}&lt;/b&gt; = &lt;b&gt;{3}&lt;/b&gt;  (难度 {4})
- &lt;size=120%&gt;&lt;color={5}&gt;&lt;b&gt;— {6} —&lt;/b&gt;&lt;/color&gt;&lt;/size&gt;</t>
+ &lt;b&gt;{0}&lt;/b&gt; + &lt;b&gt;{1}&lt;/b&gt; = &lt;b&gt;{2}&lt;/b&gt; 
+(难度 {3}) 
+&lt;size=120%&gt;&lt;color={4}&gt;&lt;b&gt;— {5} —&lt;/b&gt;&lt;/color&gt;&lt;/size&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;size=150%&gt;&lt;b&gt;[ {0} ]&lt;/b&gt;&lt;/size&gt;
- D{1}: &lt;b&gt;{0}&lt;/b&gt; + Attribute: &lt;b&gt;{2}&lt;/b&gt; = &lt;b&gt;{3}&lt;/b&gt;  (Difficulty {4})
- &lt;size=120%&gt;&lt;color={5}&gt;&lt;b&gt;— {6} —&lt;/b&gt;&lt;/color&gt;&lt;/size&gt;</t>
+ &lt;b&gt;{0}&lt;/b&gt; + &lt;b&gt;{1}&lt;/b&gt; = &lt;b&gt;{2}&lt;/b&gt;  
+(Difficulty {3}) 
+&lt;size=120%&gt;&lt;color={4}&gt;&lt;b&gt;— {5} —&lt;/b&gt;&lt;/color&gt;&lt;/size&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;size=150%&gt;&lt;b&gt;[ {0} ]&lt;/b&gt;&lt;/size&gt;
- D{1}: &lt;b&gt;{0}&lt;/b&gt; + 属性: &lt;b&gt;{2}&lt;/b&gt; = &lt;b&gt;{3}&lt;/b&gt;  (難易度 {4})
- &lt;size=120%&gt;&lt;color={5}&gt;&lt;b&gt;— {6} —&lt;/b&gt;&lt;/color&gt;&lt;/size&gt;</t>
+ &lt;b&gt;{0}&lt;/b&gt; + &lt;b&gt;{1}&lt;/b&gt; = &lt;b&gt;{2}&lt;/b&gt;  
+(難易度 {3}) 
+&lt;size=120%&gt;&lt;color={4}&gt;&lt;b&gt;— {5} —&lt;/b&gt;&lt;/color&gt;&lt;/size&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;size=150%&gt;&lt;b&gt;[ {0} ]&lt;/b&gt;&lt;/size&gt;
- D{1}: &lt;b&gt;{0}&lt;/b&gt; + 屬性: &lt;b&gt;{2}&lt;/b&gt; = &lt;b&gt;{3}&lt;/b&gt;  (難度 {4})
- &lt;size=120%&gt;&lt;color={5}&gt;&lt;b&gt;— {6} —&lt;/b&gt;&lt;/color&gt;&lt;/size&gt;</t>
+ &lt;b&gt;{0}&lt;/b&gt; + &lt;b&gt;{1}&lt;/b&gt; = &lt;b&gt;{2}&lt;/b&gt;  
+(難度 {3}) 
+&lt;size=120%&gt;&lt;color={4}&gt;&lt;b&gt;— {5} —&lt;/b&gt;&lt;/color&gt;&lt;/size&gt;</t>
   </si>
   <si>
     <t>UI.Common.Success</t>
@@ -664,12 +682,17 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7B2" tint="0"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -684,8 +707,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -696,8 +726,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="50" customWidth="1" style="2"/>
+    <col min="5" max="5" width="50" customWidth="1" style="2"/>
+    <col min="6" max="6" width="50" customWidth="1" style="2"/>
+    <col min="7" max="7" width="50" customWidth="1" style="2"/>
+    <col min="8" max="8" width="50" customWidth="1" style="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
@@ -709,19 +749,19 @@
       <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -735,19 +775,19 @@
       <c r="C2" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="0" t="s">
+      <c r="H2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -755,739 +795,628 @@
       <c r="B3" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="F3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="G3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="H3" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="H3" s="0" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="0" t="s">
+      <c r="F4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="G4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="0" t="s">
+      <c r="H4" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="H4" s="0" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="0" t="s">
+      <c r="F5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="G5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="H5" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="H5" s="0" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="0" t="s">
+      <c r="F6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="G6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="0" t="s">
+      <c r="H6" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="H6" s="0" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="0" t="s">
+      <c r="F7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="G7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="0" t="s">
+      <c r="H7" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="H7" s="0" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="0" t="s">
+      <c r="F8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="G8" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G8" s="0" t="s">
+      <c r="H8" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="H8" s="0" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="0" t="s">
+      <c r="F9" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="G9" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G9" s="0" t="s">
+      <c r="H9" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="H9" s="0" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="0" t="s">
+      <c r="F10" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="G10" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G10" s="0" t="s">
+      <c r="H10" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="H10" s="0" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="0" t="s">
+      <c r="F11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F11" s="0" t="s">
+      <c r="G11" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G11" s="0" t="s">
+      <c r="H11" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="H11" s="0" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D12" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="0" t="s">
+      <c r="F12" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="G12" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G12" s="0" t="s">
+      <c r="H12" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="H12" s="0" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D13" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="0" t="s">
+      <c r="F13" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F13" s="0" t="s">
+      <c r="G13" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="G13" s="0" t="s">
+      <c r="H13" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="H13" s="0" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D14" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="0" t="s">
+      <c r="F14" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F14" s="0" t="s">
+      <c r="G14" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G14" s="0" t="s">
+      <c r="H14" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="H14" s="0" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D15" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="0" t="s">
+      <c r="F15" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F15" s="0" t="s">
+      <c r="G15" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="G15" s="0" t="s">
+      <c r="H15" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="H15" s="0" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D16" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="0" t="s">
+      <c r="F16" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F16" s="0" t="s">
+      <c r="G16" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="G16" s="0" t="s">
+      <c r="H16" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="H16" s="0" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D17" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="0" t="s">
+      <c r="F17" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F17" s="0" t="s">
+      <c r="G17" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G17" s="0" t="s">
+      <c r="H17" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="H17" s="0" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D18" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="0" t="s">
+      <c r="F18" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="F18" s="0" t="s">
+      <c r="G18" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="G18" s="0" t="s">
+      <c r="H18" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="H18" s="0" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D19" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="0" t="s">
+      <c r="F19" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F19" s="0" t="s">
+      <c r="G19" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G19" s="0" t="s">
+      <c r="H19" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="H19" s="0" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D20" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" s="0" t="s">
+      <c r="F20" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="F20" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="G20" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="H20" s="0" t="s">
-        <v>97</v>
+      <c r="G20" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D21" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E21" s="0" t="s">
+      <c r="F21" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F21" s="0" t="s">
+      <c r="G21" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="G21" s="0" t="s">
+      <c r="H21" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="H21" s="0" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D22" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" s="0" t="s">
+      <c r="F22" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="F22" s="0" t="s">
+      <c r="G22" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="G22" s="0" t="s">
-        <v>107</v>
-      </c>
-      <c r="H22" s="0" t="s">
-        <v>105</v>
+      <c r="H22" s="2" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D23" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" s="0" t="s">
+      <c r="F23" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="F23" s="0" t="s">
+      <c r="G23" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="G23" s="0" t="s">
+      <c r="H23" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="H23" s="0" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D24" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" s="0" t="s">
+      <c r="F24" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="F24" s="0" t="s">
+      <c r="G24" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="G24" s="0" t="s">
+      <c r="H24" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="H24" s="0" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D25" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" s="0" t="s">
+      <c r="F25" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="F25" s="0" t="s">
+      <c r="G25" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G25" s="0" t="s">
-        <v>121</v>
-      </c>
-      <c r="H25" s="0" t="s">
-        <v>119</v>
+      <c r="H25" s="2" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D26" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" s="0" t="s">
+      <c r="F26" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="F26" s="0" t="s">
-        <v>124</v>
-      </c>
-      <c r="G26" s="0" t="s">
-        <v>123</v>
-      </c>
-      <c r="H26" s="0" t="s">
-        <v>123</v>
+      <c r="G26" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="D27" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E27" s="0" t="s">
+      <c r="F27" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="F27" s="0" t="s">
+      <c r="G27" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="G27" s="0" t="s">
+      <c r="H27" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="H27" s="0" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="D28" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" s="0" t="s">
+      <c r="F28" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="F28" s="0" t="s">
+      <c r="G28" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="G28" s="0" t="s">
+      <c r="H28" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="H28" s="0" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D29" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" s="0" t="s">
+      <c r="F29" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="F29" s="0" t="s">
+      <c r="G29" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="G29" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="H29" s="0" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="D30" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" s="0" t="s">
+      <c r="F30" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="F30" s="0" t="s">
+      <c r="G30" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="G30" s="0" t="s">
+      <c r="H30" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="H30" s="0" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="0" t="s">
+        <v>143</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D31" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E31" s="0" t="s">
+      <c r="F31" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="F31" s="0" t="s">
+      <c r="G31" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="G31" s="0" t="s">
+      <c r="H31" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="H31" s="0" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D32" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E32" s="0" t="s">
+      <c r="F32" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="F32" s="0" t="s">
+      <c r="G32" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="H32" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="G32" s="0" t="s">
-        <v>150</v>
-      </c>
-      <c r="H32" s="0" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="0" t="s">
+        <v>152</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="D33" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E33" s="0" t="s">
+      <c r="F33" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="F33" s="0" t="s">
+      <c r="G33" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="G33" s="0" t="s">
-        <v>156</v>
-      </c>
-      <c r="H33" s="0" t="s">
-        <v>154</v>
+      <c r="H33" s="2" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="0" t="s">
+        <v>156</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D34" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" s="0" t="s">
+      <c r="F34" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="F34" s="0" t="s">
+      <c r="G34" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="G34" s="0" t="s">
-        <v>160</v>
-      </c>
-      <c r="H34" s="0" t="s">
-        <v>158</v>
+      <c r="H34" s="2" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="0" t="s">
+        <v>160</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D35" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E35" s="0" t="s">
+      <c r="F35" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="F35" s="0" t="s">
+      <c r="G35" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="G35" s="0" t="s">
-        <v>162</v>
-      </c>
-      <c r="H35" s="0" t="s">
-        <v>162</v>
+      <c r="H35" s="2" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="0" t="s">
-        <v>164</v>
-      </c>
-      <c r="D36" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E36" s="0" t="s">
         <v>165</v>
       </c>
-      <c r="F36" s="0" t="s">
+      <c r="D36" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="G36" s="0" t="s">
+      <c r="F36" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="H36" s="0" t="s">
-        <v>168</v>
+      <c r="G36" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D37" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E37" s="0" t="s">
+      <c r="F37" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="F37" s="0" t="s">
+      <c r="G37" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="G37" s="0" t="s">
+      <c r="H37" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="H37" s="0" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="0" t="s">
         <v>173</v>
       </c>
-      <c r="D38" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E38" s="0" t="s">
+      <c r="D38" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="F38" s="0" t="s">
+      <c r="F38" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="G38" s="0" t="s">
+      <c r="G38" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="H38" s="0" t="s">
-        <v>177</v>
+      <c r="H38" s="2" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="0" t="s">
+        <v>177</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="D39" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E39" s="0" t="s">
+      <c r="F39" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="F39" s="0" t="s">
+      <c r="G39" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="G39" s="0" t="s">
-        <v>179</v>
-      </c>
-      <c r="H39" s="0" t="s">
+      <c r="H39" s="2" t="s">
         <v>181</v>
       </c>
     </row>
@@ -1495,79 +1424,71 @@
       <c r="B40" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="D40" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E40" s="0" t="s">
+      <c r="D40" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="F40" s="0" t="s">
+      <c r="F40" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="G40" s="0" t="s">
+      <c r="G40" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H40" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="H40" s="0" t="s">
+    </row>
+    <row r="41" s="1" customFormat="1">
+      <c r="B41" s="1" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="0" t="s">
+      <c r="C41" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="D41" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E41" s="0" t="s">
+      <c r="D41" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="F41" s="0" t="s">
+      <c r="E41" s="3"/>
+      <c r="F41" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G41" s="0" t="s">
-        <v>188</v>
-      </c>
-      <c r="H41" s="0" t="s">
-        <v>188</v>
+      <c r="G41" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="0" t="s">
-        <v>190</v>
-      </c>
-      <c r="D42" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E42" s="0" t="s">
-        <v>191</v>
-      </c>
-      <c r="F42" s="0" t="s">
         <v>192</v>
       </c>
-      <c r="G42" s="0" t="s">
+      <c r="D42" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="H42" s="0" t="s">
+      <c r="F42" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="H42" s="2" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="0" t="s">
-        <v>194</v>
-      </c>
-      <c r="D43" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E43" s="0" t="s">
         <v>195</v>
       </c>
-      <c r="F43" s="0" t="s">
+      <c r="D43" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="G43" s="0" t="s">
+      <c r="F43" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="H43" s="0" t="s">
+      <c r="G43" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H43" s="2" t="s">
         <v>198</v>
       </c>
     </row>
@@ -1575,40 +1496,51 @@
       <c r="B44" s="0" t="s">
         <v>199</v>
       </c>
-      <c r="D44" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E44" s="0" t="s">
+      <c r="D44" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="F44" s="0" t="s">
+      <c r="F44" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="G44" s="0" t="s">
+      <c r="G44" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="H44" s="0" t="s">
-        <v>202</v>
+      <c r="H44" s="2" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="0" t="s">
-        <v>203</v>
-      </c>
-      <c r="D45" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E45" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="F45" s="0" t="s">
+      <c r="D45" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="G45" s="0" t="s">
+      <c r="F45" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="H45" s="0" t="s">
+      <c r="G45" s="2" t="s">
         <v>207</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Localization/翻译文本/CollectedLocalizeData.xlsx
+++ b/Assets/Localization/翻译文本/CollectedLocalizeData.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="212">
   <si>
     <t>#var</t>
   </si>
@@ -23,10 +23,10 @@
     <t>lTips1</t>
   </si>
   <si>
+    <t>lTips2</t>
+  </si>
+  <si>
     <t>zh-CN</t>
-  </si>
-  <si>
-    <t>lTips2</t>
   </si>
   <si>
     <t>en</t>
@@ -578,16 +578,7 @@
     <t>UI.Dice.RollResult</t>
   </si>
   <si>
-    <t xml:space="preserve">修改:[&lt;size=150%&gt;&lt;b&gt;[ {0} ]&lt;/b&gt;&lt;/size&gt;\n &lt;b&gt;{0}&lt;/b&gt; + &lt;b&gt;{1}&lt;/b&gt; = &lt;b&gt;{2}&lt;/b&gt;  \n(难度 {3}) \n&lt;size=120%&gt;&lt;color={4}&gt;&lt;b&gt;— {5} —&lt;/b&gt;&lt;/color&gt;&lt;/size&gt;]-&gt;[&lt;size=150%&gt;&lt;b&gt;[ {0} ]&lt;/b&gt;&lt;/size&gt;
- &lt;b&gt;{0}&lt;/b&gt; + &lt;b&gt;{1}&lt;/b&gt; = &lt;b&gt;{2}&lt;/b&gt; 
-(难度 {3}) 
-&lt;size=120%&gt;&lt;color={4}&gt;&lt;b&gt;— {5} —&lt;/b&gt;&lt;/color&gt;&lt;/size&gt;] 2026/2/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;size=150%&gt;&lt;b&gt;[ {0} ]&lt;/b&gt;&lt;/size&gt;
- &lt;b&gt;{0}&lt;/b&gt; + &lt;b&gt;{1}&lt;/b&gt; = &lt;b&gt;{2}&lt;/b&gt; 
-(难度 {3}) 
-&lt;size=120%&gt;&lt;color={4}&gt;&lt;b&gt;— {5} —&lt;/b&gt;&lt;/color&gt;&lt;/size&gt;</t>
+    <t xml:space="preserve">&lt;size=150%&gt;&lt;b&gt;[ {0} ]&lt;/b&gt;&lt;/size&gt;\n &lt;b&gt;{0}&lt;/b&gt; + &lt;b&gt;{1}&lt;/b&gt; = &lt;b&gt;{2}&lt;/b&gt;  \n(难度 {3}) \n&lt;size=120%&gt;&lt;color={4}&gt;&lt;b&gt;— {5} —&lt;/b&gt;&lt;/color&gt;&lt;/size&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;size=150%&gt;&lt;b&gt;[ {0} ]&lt;/b&gt;&lt;/size&gt;
@@ -682,17 +673,12 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7B2" tint="0"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -707,15 +693,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -728,16 +707,6 @@
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:H46"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1" style="2"/>
-    <col min="5" max="5" width="50" customWidth="1" style="2"/>
-    <col min="6" max="6" width="50" customWidth="1" style="2"/>
-    <col min="7" max="7" width="50" customWidth="1" style="2"/>
-    <col min="8" max="8" width="50" customWidth="1" style="2"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
@@ -749,19 +718,19 @@
       <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="0" t="s">
         <v>7</v>
       </c>
     </row>
@@ -775,19 +744,19 @@
       <c r="C2" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="0" t="s">
         <v>9</v>
       </c>
     </row>
@@ -795,16 +764,16 @@
       <c r="B3" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="0" t="s">
         <v>14</v>
       </c>
     </row>
@@ -812,16 +781,16 @@
       <c r="B4" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="0" t="s">
         <v>19</v>
       </c>
     </row>
@@ -829,16 +798,16 @@
       <c r="B5" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="0" t="s">
         <v>24</v>
       </c>
     </row>
@@ -846,16 +815,16 @@
       <c r="B6" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="0" t="s">
         <v>29</v>
       </c>
     </row>
@@ -863,16 +832,16 @@
       <c r="B7" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="0" t="s">
         <v>34</v>
       </c>
     </row>
@@ -880,16 +849,16 @@
       <c r="B8" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="0" t="s">
         <v>39</v>
       </c>
     </row>
@@ -897,16 +866,16 @@
       <c r="B9" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="0" t="s">
         <v>44</v>
       </c>
     </row>
@@ -914,16 +883,16 @@
       <c r="B10" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="0" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="0" t="s">
         <v>48</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="0" t="s">
         <v>49</v>
       </c>
     </row>
@@ -931,16 +900,16 @@
       <c r="B11" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="0" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="0" t="s">
         <v>53</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="0" t="s">
         <v>54</v>
       </c>
     </row>
@@ -948,16 +917,16 @@
       <c r="B12" s="0" t="s">
         <v>55</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="0" t="s">
         <v>57</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="0" t="s">
         <v>58</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" s="0" t="s">
         <v>59</v>
       </c>
     </row>
@@ -965,16 +934,16 @@
       <c r="B13" s="0" t="s">
         <v>60</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="0" t="s">
         <v>62</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="0" t="s">
         <v>63</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="0" t="s">
         <v>64</v>
       </c>
     </row>
@@ -982,16 +951,16 @@
       <c r="B14" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="0" t="s">
         <v>66</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" s="0" t="s">
         <v>69</v>
       </c>
     </row>
@@ -999,16 +968,16 @@
       <c r="B15" s="0" t="s">
         <v>70</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="0" t="s">
         <v>71</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="0" t="s">
         <v>73</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="H15" s="0" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1016,16 +985,16 @@
       <c r="B16" s="0" t="s">
         <v>75</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="0" t="s">
         <v>76</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="0" t="s">
         <v>77</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="0" t="s">
         <v>78</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="H16" s="0" t="s">
         <v>79</v>
       </c>
     </row>
@@ -1033,16 +1002,16 @@
       <c r="B17" s="0" t="s">
         <v>80</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="E17" s="0" t="s">
         <v>81</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="0" t="s">
         <v>82</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G17" s="0" t="s">
         <v>83</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="H17" s="0" t="s">
         <v>84</v>
       </c>
     </row>
@@ -1050,16 +1019,16 @@
       <c r="B18" s="0" t="s">
         <v>85</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="0" t="s">
         <v>86</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="0" t="s">
         <v>87</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="G18" s="0" t="s">
         <v>88</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="H18" s="0" t="s">
         <v>89</v>
       </c>
     </row>
@@ -1067,16 +1036,16 @@
       <c r="B19" s="0" t="s">
         <v>90</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="0" t="s">
         <v>91</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="0" t="s">
         <v>92</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="0" t="s">
         <v>93</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="H19" s="0" t="s">
         <v>94</v>
       </c>
     </row>
@@ -1084,16 +1053,16 @@
       <c r="B20" s="0" t="s">
         <v>95</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="E20" s="0" t="s">
         <v>96</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="0" t="s">
         <v>97</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="0" t="s">
         <v>96</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="H20" s="0" t="s">
         <v>96</v>
       </c>
     </row>
@@ -1101,16 +1070,16 @@
       <c r="B21" s="0" t="s">
         <v>98</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="E21" s="0" t="s">
         <v>99</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="0" t="s">
         <v>100</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="0" t="s">
         <v>101</v>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="H21" s="0" t="s">
         <v>102</v>
       </c>
     </row>
@@ -1118,16 +1087,16 @@
       <c r="B22" s="0" t="s">
         <v>103</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="0" t="s">
         <v>104</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="0" t="s">
         <v>105</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="G22" s="0" t="s">
         <v>106</v>
       </c>
-      <c r="H22" s="2" t="s">
+      <c r="H22" s="0" t="s">
         <v>104</v>
       </c>
     </row>
@@ -1135,16 +1104,16 @@
       <c r="B23" s="0" t="s">
         <v>107</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="0" t="s">
         <v>108</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="0" t="s">
         <v>109</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="G23" s="0" t="s">
         <v>110</v>
       </c>
-      <c r="H23" s="2" t="s">
+      <c r="H23" s="0" t="s">
         <v>111</v>
       </c>
     </row>
@@ -1152,16 +1121,16 @@
       <c r="B24" s="0" t="s">
         <v>112</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="E24" s="0" t="s">
         <v>113</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="0" t="s">
         <v>114</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G24" s="0" t="s">
         <v>115</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="H24" s="0" t="s">
         <v>116</v>
       </c>
     </row>
@@ -1169,16 +1138,16 @@
       <c r="B25" s="0" t="s">
         <v>117</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="E25" s="0" t="s">
         <v>118</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="0" t="s">
         <v>119</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="G25" s="0" t="s">
         <v>120</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="H25" s="0" t="s">
         <v>118</v>
       </c>
     </row>
@@ -1186,16 +1155,16 @@
       <c r="B26" s="0" t="s">
         <v>121</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="E26" s="0" t="s">
         <v>122</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="0" t="s">
         <v>123</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="G26" s="0" t="s">
         <v>122</v>
       </c>
-      <c r="H26" s="2" t="s">
+      <c r="H26" s="0" t="s">
         <v>122</v>
       </c>
     </row>
@@ -1203,16 +1172,16 @@
       <c r="B27" s="0" t="s">
         <v>124</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="E27" s="0" t="s">
         <v>125</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" s="0" t="s">
         <v>126</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="G27" s="0" t="s">
         <v>127</v>
       </c>
-      <c r="H27" s="2" t="s">
+      <c r="H27" s="0" t="s">
         <v>128</v>
       </c>
     </row>
@@ -1220,16 +1189,16 @@
       <c r="B28" s="0" t="s">
         <v>129</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="E28" s="0" t="s">
         <v>130</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="F28" s="0" t="s">
         <v>131</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="G28" s="0" t="s">
         <v>132</v>
       </c>
-      <c r="H28" s="2" t="s">
+      <c r="H28" s="0" t="s">
         <v>133</v>
       </c>
     </row>
@@ -1237,16 +1206,16 @@
       <c r="B29" s="0" t="s">
         <v>134</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="E29" s="0" t="s">
         <v>135</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="F29" s="0" t="s">
         <v>136</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="G29" s="0" t="s">
         <v>135</v>
       </c>
-      <c r="H29" s="2" t="s">
+      <c r="H29" s="0" t="s">
         <v>137</v>
       </c>
     </row>
@@ -1254,16 +1223,16 @@
       <c r="B30" s="0" t="s">
         <v>138</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="E30" s="0" t="s">
         <v>139</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F30" s="0" t="s">
         <v>140</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="G30" s="0" t="s">
         <v>141</v>
       </c>
-      <c r="H30" s="2" t="s">
+      <c r="H30" s="0" t="s">
         <v>142</v>
       </c>
     </row>
@@ -1271,16 +1240,16 @@
       <c r="B31" s="0" t="s">
         <v>143</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="E31" s="0" t="s">
         <v>144</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="F31" s="0" t="s">
         <v>145</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="G31" s="0" t="s">
         <v>146</v>
       </c>
-      <c r="H31" s="2" t="s">
+      <c r="H31" s="0" t="s">
         <v>147</v>
       </c>
     </row>
@@ -1288,16 +1257,16 @@
       <c r="B32" s="0" t="s">
         <v>148</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="E32" s="0" t="s">
         <v>149</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="F32" s="0" t="s">
         <v>150</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="G32" s="0" t="s">
         <v>149</v>
       </c>
-      <c r="H32" s="2" t="s">
+      <c r="H32" s="0" t="s">
         <v>151</v>
       </c>
     </row>
@@ -1305,16 +1274,16 @@
       <c r="B33" s="0" t="s">
         <v>152</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="E33" s="0" t="s">
         <v>153</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="F33" s="0" t="s">
         <v>154</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="G33" s="0" t="s">
         <v>155</v>
       </c>
-      <c r="H33" s="2" t="s">
+      <c r="H33" s="0" t="s">
         <v>153</v>
       </c>
     </row>
@@ -1322,16 +1291,16 @@
       <c r="B34" s="0" t="s">
         <v>156</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="E34" s="0" t="s">
         <v>157</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="F34" s="0" t="s">
         <v>158</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="G34" s="0" t="s">
         <v>159</v>
       </c>
-      <c r="H34" s="2" t="s">
+      <c r="H34" s="0" t="s">
         <v>157</v>
       </c>
     </row>
@@ -1339,16 +1308,16 @@
       <c r="B35" s="0" t="s">
         <v>160</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="E35" s="0" t="s">
         <v>161</v>
       </c>
-      <c r="F35" s="2" t="s">
+      <c r="F35" s="0" t="s">
         <v>162</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="G35" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="H35" s="2" t="s">
+      <c r="H35" s="0" t="s">
         <v>164</v>
       </c>
     </row>
@@ -1356,16 +1325,16 @@
       <c r="B36" s="0" t="s">
         <v>165</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="E36" s="0" t="s">
         <v>166</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="F36" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="G36" s="0" t="s">
         <v>166</v>
       </c>
-      <c r="H36" s="2" t="s">
+      <c r="H36" s="0" t="s">
         <v>166</v>
       </c>
     </row>
@@ -1373,16 +1342,16 @@
       <c r="B37" s="0" t="s">
         <v>168</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="E37" s="0" t="s">
         <v>169</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="F37" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="G37" s="0" t="s">
         <v>171</v>
       </c>
-      <c r="H37" s="2" t="s">
+      <c r="H37" s="0" t="s">
         <v>172</v>
       </c>
     </row>
@@ -1390,16 +1359,16 @@
       <c r="B38" s="0" t="s">
         <v>173</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="E38" s="0" t="s">
         <v>174</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="F38" s="0" t="s">
         <v>175</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="G38" s="0" t="s">
         <v>176</v>
       </c>
-      <c r="H38" s="2" t="s">
+      <c r="H38" s="0" t="s">
         <v>174</v>
       </c>
     </row>
@@ -1407,16 +1376,16 @@
       <c r="B39" s="0" t="s">
         <v>177</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="E39" s="0" t="s">
         <v>178</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="F39" s="0" t="s">
         <v>179</v>
       </c>
-      <c r="G39" s="2" t="s">
+      <c r="G39" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="H39" s="2" t="s">
+      <c r="H39" s="0" t="s">
         <v>181</v>
       </c>
     </row>
@@ -1424,123 +1393,119 @@
       <c r="B40" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="E40" s="0" t="s">
         <v>183</v>
       </c>
-      <c r="F40" s="2" t="s">
+      <c r="F40" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="G40" s="2" t="s">
+      <c r="G40" s="0" t="s">
         <v>183</v>
       </c>
-      <c r="H40" s="2" t="s">
+      <c r="H40" s="0" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="41" s="1" customFormat="1">
-      <c r="B41" s="1" t="s">
+    <row r="41">
+      <c r="B41" s="0" t="s">
         <v>186</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="E41" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="F41" s="0" t="s">
         <v>188</v>
       </c>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3" t="s">
+      <c r="G41" s="0" t="s">
         <v>189</v>
       </c>
-      <c r="G41" s="3" t="s">
+      <c r="H41" s="0" t="s">
         <v>190</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="E42" s="0" t="s">
         <v>192</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="F42" s="0" t="s">
         <v>193</v>
       </c>
-      <c r="F42" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>193</v>
+      <c r="G42" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="H42" s="0" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="0" t="s">
+        <v>194</v>
+      </c>
+      <c r="E43" s="0" t="s">
         <v>195</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="F43" s="0" t="s">
         <v>196</v>
       </c>
-      <c r="F43" s="2" t="s">
+      <c r="G43" s="0" t="s">
         <v>197</v>
       </c>
-      <c r="G43" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>198</v>
+      <c r="H43" s="0" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="0" t="s">
+        <v>198</v>
+      </c>
+      <c r="E44" s="0" t="s">
         <v>199</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="F44" s="0" t="s">
         <v>200</v>
       </c>
-      <c r="F44" s="2" t="s">
+      <c r="G44" s="0" t="s">
         <v>201</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="H44" s="0" t="s">
         <v>202</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="0" t="s">
+        <v>203</v>
+      </c>
+      <c r="E45" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="F45" s="0" t="s">
         <v>205</v>
       </c>
-      <c r="F45" s="2" t="s">
+      <c r="G45" s="0" t="s">
         <v>206</v>
       </c>
-      <c r="G45" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>207</v>
+      <c r="H45" s="0" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="E46" s="0" t="s">
         <v>208</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="F46" s="0" t="s">
         <v>209</v>
       </c>
-      <c r="F46" s="2" t="s">
+      <c r="G46" s="0" t="s">
         <v>210</v>
       </c>
-      <c r="G46" s="2" t="s">
+      <c r="H46" s="0" t="s">
         <v>211</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>212</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Localization/翻译文本/CollectedLocalizeData.xlsx
+++ b/Assets/Localization/翻译文本/CollectedLocalizeData.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="213">
   <si>
     <t>#var</t>
   </si>
@@ -578,7 +578,19 @@
     <t>UI.Dice.RollResult</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;size=150%&gt;&lt;b&gt;[ {0} ]&lt;/b&gt;&lt;/size&gt;\n &lt;b&gt;{0}&lt;/b&gt; + &lt;b&gt;{1}&lt;/b&gt; = &lt;b&gt;{2}&lt;/b&gt;  \n(难度 {3}) \n&lt;size=120%&gt;&lt;color={4}&gt;&lt;b&gt;— {5} —&lt;/b&gt;&lt;/color&gt;&lt;/size&gt;</t>
+    <t xml:space="preserve">修改:[&lt;size=150%&gt;&lt;b&gt;[ {0} ]&lt;/b&gt;&lt;/size&gt;
+&lt;b&gt;{0}&lt;/b&gt; + &lt;b&gt;{1}&lt;/b&gt; = &lt;b&gt;{2}&lt;/b&gt;
+(难度 {3})
+&lt;size=120%&gt;&lt;color={4}&gt;&lt;b&gt;— {5} —&lt;/b&gt;&lt;/color&gt;&lt;/size&gt;]-&gt;[&lt;size=150%&gt;&lt;b&gt;[ {0} ]&lt;/b&gt;&lt;/size&gt;
+ &lt;b&gt;{0}&lt;/b&gt; + &lt;b&gt;{1}&lt;/b&gt; = &lt;b&gt;{2}&lt;/b&gt;  
+(难度 {3}) 
+&lt;size=120%&gt;&lt;color={4}&gt;&lt;b&gt;— {5} —&lt;/b&gt;&lt;/color&gt;&lt;/size&gt;] 2026/3/1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;size=150%&gt;&lt;b&gt;[ {0} ]&lt;/b&gt;&lt;/size&gt;
+ &lt;b&gt;{0}&lt;/b&gt; + &lt;b&gt;{1}&lt;/b&gt; = &lt;b&gt;{2}&lt;/b&gt;  
+(难度 {3}) 
+&lt;size=120%&gt;&lt;color={4}&gt;&lt;b&gt;— {5} —&lt;/b&gt;&lt;/color&gt;&lt;/size&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;size=150%&gt;&lt;b&gt;[ {0} ]&lt;/b&gt;&lt;/size&gt;
@@ -1410,102 +1422,108 @@
       <c r="B41" s="0" t="s">
         <v>186</v>
       </c>
+      <c r="C41" s="0" t="s">
+        <v>187</v>
+      </c>
+      <c r="D41" s="0" t="s">
+        <v>187</v>
+      </c>
       <c r="E41" s="0" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F41" s="0" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G41" s="0" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H41" s="0" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="0" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E42" s="0" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F42" s="0" t="s">
+        <v>194</v>
+      </c>
+      <c r="G42" s="0" t="s">
         <v>193</v>
       </c>
-      <c r="G42" s="0" t="s">
-        <v>192</v>
-      </c>
       <c r="H42" s="0" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="0" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G43" s="0" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H43" s="0" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="0" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G44" s="0" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H44" s="0" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="0" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G45" s="0" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="0" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G46" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H46" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Localization/翻译文本/CollectedLocalizeData.xlsx
+++ b/Assets/Localization/翻译文本/CollectedLocalizeData.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="219">
   <si>
     <t>#var</t>
   </si>
@@ -543,6 +543,24 @@
   </si>
   <si>
     <t>リセット</t>
+  </si>
+  <si>
+    <t>UI.SavePanel.Quit</t>
+  </si>
+  <si>
+    <t>新增 2026/3/3</t>
+  </si>
+  <si>
+    <t>新增 2026/3/3AI</t>
+  </si>
+  <si>
+    <t>退出</t>
+  </si>
+  <si>
+    <t>Exit</t>
+  </si>
+  <si>
+    <t>終了</t>
   </si>
   <si>
     <t>UI.Dice.DetailText</t>
@@ -579,18 +597,12 @@
   </si>
   <si>
     <t xml:space="preserve">修改:[&lt;size=150%&gt;&lt;b&gt;[ {0} ]&lt;/b&gt;&lt;/size&gt;
-&lt;b&gt;{0}&lt;/b&gt; + &lt;b&gt;{1}&lt;/b&gt; = &lt;b&gt;{2}&lt;/b&gt;
-(难度 {3})
-&lt;size=120%&gt;&lt;color={4}&gt;&lt;b&gt;— {5} —&lt;/b&gt;&lt;/color&gt;&lt;/size&gt;]-&gt;[&lt;size=150%&gt;&lt;b&gt;[ {0} ]&lt;/b&gt;&lt;/size&gt;
  &lt;b&gt;{0}&lt;/b&gt; + &lt;b&gt;{1}&lt;/b&gt; = &lt;b&gt;{2}&lt;/b&gt;  
 (难度 {3}) 
-&lt;size=120%&gt;&lt;color={4}&gt;&lt;b&gt;— {5} —&lt;/b&gt;&lt;/color&gt;&lt;/size&gt;] 2026/3/1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;size=150%&gt;&lt;b&gt;[ {0} ]&lt;/b&gt;&lt;/size&gt;
- &lt;b&gt;{0}&lt;/b&gt; + &lt;b&gt;{1}&lt;/b&gt; = &lt;b&gt;{2}&lt;/b&gt;  
-(难度 {3}) 
-&lt;size=120%&gt;&lt;color={4}&gt;&lt;b&gt;— {5} —&lt;/b&gt;&lt;/color&gt;&lt;/size&gt;</t>
+&lt;size=120%&gt;&lt;color={4}&gt;&lt;b&gt;— {5} —&lt;/b&gt;&lt;/color&gt;&lt;/size&gt;]-&gt;[&lt;size=150%&gt;&lt;b&gt;[ {0} ]&lt;/b&gt;&lt;/size&gt; &lt;b&gt;{0}&lt;/b&gt; + &lt;b&gt;{1}&lt;/b&gt; = &lt;b&gt;{2}&lt;/b&gt; (难度 {3}) &lt;size=120%&gt;&lt;color={4}&gt;&lt;b&gt;— {5} —&lt;/b&gt;&lt;/color&gt;&lt;/size&gt;] 2026/3/3</t>
+  </si>
+  <si>
+    <t>&lt;size=150%&gt;&lt;b&gt;[ {0} ]&lt;/b&gt;&lt;/size&gt; &lt;b&gt;{0}&lt;/b&gt; + &lt;b&gt;{1}&lt;/b&gt; = &lt;b&gt;{2}&lt;/b&gt; (难度 {3}) &lt;size=120%&gt;&lt;color={4}&gt;&lt;b&gt;— {5} —&lt;/b&gt;&lt;/color&gt;&lt;/size&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;size=150%&gt;&lt;b&gt;[ {0} ]&lt;/b&gt;&lt;/size&gt;
@@ -717,7 +729,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1388,54 +1400,54 @@
       <c r="B39" s="0" t="s">
         <v>177</v>
       </c>
+      <c r="C39" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="D39" s="0" t="s">
+        <v>179</v>
+      </c>
       <c r="E39" s="0" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G39" s="0" t="s">
+        <v>182</v>
+      </c>
+      <c r="H39" s="0" t="s">
         <v>180</v>
-      </c>
-      <c r="H39" s="0" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="0" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G40" s="0" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H40" s="0" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="0" t="s">
-        <v>186</v>
-      </c>
-      <c r="C41" s="0" t="s">
-        <v>187</v>
-      </c>
-      <c r="D41" s="0" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F41" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="G41" s="0" t="s">
         <v>189</v>
-      </c>
-      <c r="G41" s="0" t="s">
-        <v>190</v>
       </c>
       <c r="H41" s="0" t="s">
         <v>191</v>
@@ -1445,85 +1457,108 @@
       <c r="B42" s="0" t="s">
         <v>192</v>
       </c>
+      <c r="C42" s="0" t="s">
+        <v>193</v>
+      </c>
+      <c r="D42" s="0" t="s">
+        <v>193</v>
+      </c>
       <c r="E42" s="0" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F42" s="0" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G42" s="0" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="H42" s="0" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="0" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G43" s="0" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H43" s="0" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="0" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G44" s="0" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H44" s="0" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="0" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G45" s="0" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="0" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G46" s="0" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H46" s="0" t="s">
-        <v>212</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="E47" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="F47" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="G47" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="H47" s="0" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>
